--- a/MAA-YOJANA-PACKAGELIST/Accounts/transactionDetails.xlsx
+++ b/MAA-YOJANA-PACKAGELIST/Accounts/transactionDetails.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="142">
   <si>
     <t>T.ID</t>
   </si>
@@ -348,6 +348,102 @@
   </si>
   <si>
     <t>Teena</t>
+  </si>
+  <si>
+    <t>T13072540491051</t>
+  </si>
+  <si>
+    <t>Ashok Soni</t>
+  </si>
+  <si>
+    <t>T14072540514896</t>
+  </si>
+  <si>
+    <t>Meena Nayak</t>
+  </si>
+  <si>
+    <t>T17072540579046</t>
+  </si>
+  <si>
+    <t>T17072540592513</t>
+  </si>
+  <si>
+    <t>Laxman Lal Kumawat</t>
+  </si>
+  <si>
+    <t>T20072540659744</t>
+  </si>
+  <si>
+    <t>Shanti Devi</t>
+  </si>
+  <si>
+    <t>T26072540825361</t>
+  </si>
+  <si>
+    <t>Surta</t>
+  </si>
+  <si>
+    <t>T29072540882223</t>
+  </si>
+  <si>
+    <t>SOHAN NAYAK</t>
+  </si>
+  <si>
+    <t>T18082541376751</t>
+  </si>
+  <si>
+    <t>T28082541645434</t>
+  </si>
+  <si>
+    <t>T31082541723442</t>
+  </si>
+  <si>
+    <t>Sanwar Lal</t>
+  </si>
+  <si>
+    <t>T08092541911757</t>
+  </si>
+  <si>
+    <t>Rohit Prajapat</t>
+  </si>
+  <si>
+    <t>T08092541928279</t>
+  </si>
+  <si>
+    <t>Chetan Nayak</t>
+  </si>
+  <si>
+    <t>T10092541967215</t>
+  </si>
+  <si>
+    <t>T10092541978166</t>
+  </si>
+  <si>
+    <t>Rupa Devi Khati</t>
+  </si>
+  <si>
+    <t>T14092542090919</t>
+  </si>
+  <si>
+    <t>Chhagani Devi</t>
+  </si>
+  <si>
+    <t>T15092542137214</t>
+  </si>
+  <si>
+    <t>Ramkishan Mali</t>
+  </si>
+  <si>
+    <t>T16092542158336</t>
+  </si>
+  <si>
+    <t>Sulochana Devi</t>
+  </si>
+  <si>
+    <t>T17092542188793</t>
+  </si>
+  <si>
+    <t>Shiv Ji Ram Meena</t>
   </si>
 </sst>
 </file>
@@ -357,7 +453,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -475,13 +571,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF74D3B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -524,7 +641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -599,6 +716,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -611,25 +735,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFF74D3B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -931,7 +1058,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="7" bestFit="1" customWidth="1"/>
@@ -1013,7 +1140,7 @@
       <c r="A3" s="22">
         <v>45674</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="57" t="s">
         <v>35</v>
       </c>
       <c r="C3" s="24" t="s">
@@ -1150,7 +1277,9 @@
       <c r="D7" s="12">
         <v>15000</v>
       </c>
-      <c r="E7" s="12"/>
+      <c r="E7" s="12">
+        <v>0</v>
+      </c>
       <c r="F7" s="15">
         <f t="shared" si="2"/>
         <v>15000</v>
@@ -1390,7 +1519,7 @@
         <v>20790</v>
       </c>
       <c r="I14" s="30" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1498,22 +1627,22 @@
         <v>51</v>
       </c>
       <c r="D18" s="32">
-        <v>53200</v>
+        <v>46600</v>
       </c>
       <c r="E18" s="30">
         <v>26000</v>
       </c>
       <c r="F18" s="33">
         <f t="shared" si="2"/>
-        <v>79200</v>
+        <v>72600</v>
       </c>
       <c r="G18" s="34">
         <f t="shared" si="0"/>
-        <v>7920</v>
+        <v>7260</v>
       </c>
       <c r="H18" s="34">
         <f t="shared" si="1"/>
-        <v>71280</v>
+        <v>65340</v>
       </c>
       <c r="I18" s="30" t="s">
         <v>30</v>
@@ -1708,7 +1837,7 @@
         <v>29700</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1754,22 +1883,22 @@
         <v>66</v>
       </c>
       <c r="D26" s="17">
-        <v>53200</v>
+        <v>46600</v>
       </c>
       <c r="E26" s="17">
         <v>26000</v>
       </c>
       <c r="F26" s="17">
         <f>D26+E26</f>
-        <v>79200</v>
+        <v>72600</v>
       </c>
       <c r="G26" s="17">
         <f t="shared" si="0"/>
-        <v>7920</v>
+        <v>7260</v>
       </c>
       <c r="H26" s="17">
         <f t="shared" si="1"/>
-        <v>71280</v>
+        <v>65340</v>
       </c>
       <c r="I26" s="17" t="s">
         <v>30</v>
@@ -1828,11 +1957,11 @@
         <v>5000</v>
       </c>
       <c r="G28" s="41">
-        <f t="shared" ref="G28:G45" si="3">F28*10/100</f>
+        <f t="shared" ref="G28:G44" si="3">F28*10/100</f>
         <v>500</v>
       </c>
       <c r="H28" s="41">
-        <f t="shared" ref="H28:H45" si="4">F28-G28</f>
+        <f t="shared" ref="H28:H44" si="4">F28-G28</f>
         <v>4500</v>
       </c>
       <c r="I28" s="40" t="s">
@@ -1884,9 +2013,11 @@
       <c r="D30" s="39">
         <v>5000</v>
       </c>
-      <c r="E30" s="17"/>
+      <c r="E30" s="17">
+        <v>0</v>
+      </c>
       <c r="F30" s="40">
-        <f t="shared" ref="F30:F48" si="5">D30+E30</f>
+        <f t="shared" ref="F30:F44" si="5">D30+E30</f>
         <v>5000</v>
       </c>
       <c r="G30" s="41">
@@ -1914,7 +2045,9 @@
       <c r="D31" s="39">
         <v>5000</v>
       </c>
-      <c r="E31" s="17"/>
+      <c r="E31" s="17">
+        <v>0</v>
+      </c>
       <c r="F31" s="40">
         <f t="shared" si="5"/>
         <v>5000</v>
@@ -1944,7 +2077,9 @@
       <c r="D32" s="44">
         <v>15000</v>
       </c>
-      <c r="E32" s="43"/>
+      <c r="E32" s="43">
+        <v>0</v>
+      </c>
       <c r="F32" s="45">
         <f t="shared" si="5"/>
         <v>15000</v>
@@ -1961,7 +2096,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="42">
         <v>45781</v>
       </c>
@@ -1993,7 +2128,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="42">
         <v>45785</v>
       </c>
@@ -2025,7 +2160,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="42">
         <v>45787</v>
       </c>
@@ -2057,7 +2192,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="42">
         <v>45796</v>
       </c>
@@ -2086,10 +2221,10 @@
         <v>13500</v>
       </c>
       <c r="I36" s="43" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="42">
         <v>45802</v>
       </c>
@@ -2118,10 +2253,10 @@
         <v>13500</v>
       </c>
       <c r="I37" s="43" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="42">
         <v>45808</v>
       </c>
@@ -2134,7 +2269,9 @@
       <c r="D38" s="47">
         <v>15000</v>
       </c>
-      <c r="E38" s="43"/>
+      <c r="E38" s="43">
+        <v>0</v>
+      </c>
       <c r="F38" s="45">
         <f t="shared" si="5"/>
         <v>15000</v>
@@ -2148,524 +2285,1119 @@
         <v>13500</v>
       </c>
       <c r="I38" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="J38" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="K38" s="51"/>
-      <c r="L38" s="51"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="57">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="49">
         <v>45812</v>
       </c>
-      <c r="B39" s="58" t="s">
+      <c r="B39" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="58" t="s">
+      <c r="C39" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="D39" s="58">
+      <c r="D39" s="50">
         <v>15000</v>
       </c>
-      <c r="E39" s="58"/>
-      <c r="F39" s="59">
+      <c r="E39" s="50">
+        <v>0</v>
+      </c>
+      <c r="F39" s="51">
         <f t="shared" si="5"/>
         <v>15000</v>
       </c>
-      <c r="G39" s="60">
+      <c r="G39" s="52">
         <f t="shared" si="3"/>
         <v>1500</v>
       </c>
-      <c r="H39" s="60">
+      <c r="H39" s="52">
         <f t="shared" si="4"/>
         <v>13500</v>
       </c>
-      <c r="I39" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="J39" s="9"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="57">
+      <c r="I39" s="50" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="49">
         <v>45836</v>
       </c>
-      <c r="B40" s="58" t="s">
+      <c r="B40" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="C40" s="58" t="s">
+      <c r="C40" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="D40" s="58">
+      <c r="D40" s="50">
         <v>12000</v>
       </c>
-      <c r="E40" s="58">
+      <c r="E40" s="50">
         <v>5000</v>
       </c>
-      <c r="F40" s="59">
+      <c r="F40" s="51">
         <f t="shared" si="5"/>
         <v>17000</v>
       </c>
-      <c r="G40" s="60">
+      <c r="G40" s="52">
         <f t="shared" si="3"/>
         <v>1700</v>
       </c>
-      <c r="H40" s="60">
+      <c r="H40" s="52">
         <f t="shared" si="4"/>
         <v>15300</v>
       </c>
-      <c r="I40" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="57">
+      <c r="I40" s="50" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="49">
         <v>45838</v>
       </c>
-      <c r="B41" s="58" t="s">
+      <c r="B41" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="58" t="s">
+      <c r="C41" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="D41" s="58">
+      <c r="D41" s="50">
         <v>26300</v>
       </c>
-      <c r="E41" s="58">
+      <c r="E41" s="50">
         <v>10000</v>
       </c>
-      <c r="F41" s="59">
+      <c r="F41" s="51">
         <f t="shared" si="5"/>
         <v>36300</v>
       </c>
-      <c r="G41" s="60">
+      <c r="G41" s="52">
         <f t="shared" si="3"/>
         <v>3630</v>
       </c>
-      <c r="H41" s="60">
+      <c r="H41" s="52">
         <f t="shared" si="4"/>
         <v>32670</v>
       </c>
-      <c r="I41" s="58" t="s">
+      <c r="I41" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="10" t="str">
-        <f>"Dr " &amp; SUMIF(I2:I70,"paid",G2:G70)</f>
-        <v>Dr 66695</v>
-      </c>
-      <c r="K41" s="3" t="str">
-        <f>"Cr " &amp; SUMIF(I2:I70,"pending",G2:G70)</f>
-        <v>Cr 40795</v>
-      </c>
-      <c r="L41" s="4">
-        <f>SUM(G2:G70)</f>
-        <v>107490</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="53">
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="59">
         <v>45839</v>
       </c>
-      <c r="B42" s="54" t="s">
+      <c r="B42" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="54" t="s">
+      <c r="C42" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="D42" s="54">
+      <c r="D42" s="60">
         <v>15600</v>
       </c>
-      <c r="E42" s="54">
+      <c r="E42" s="60">
         <v>10000</v>
       </c>
-      <c r="F42" s="55">
+      <c r="F42" s="61">
         <f t="shared" si="5"/>
         <v>25600</v>
       </c>
-      <c r="G42" s="56">
+      <c r="G42" s="62">
         <f t="shared" si="3"/>
         <v>2560</v>
       </c>
-      <c r="H42" s="56">
+      <c r="H42" s="62">
         <f t="shared" si="4"/>
         <v>23040</v>
       </c>
-      <c r="I42" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="J42" s="48"/>
-      <c r="K42" s="49"/>
-      <c r="L42" s="49"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="53">
+      <c r="I42" s="60" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="59">
         <v>45840</v>
       </c>
-      <c r="B43" s="54" t="s">
+      <c r="B43" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="C43" s="54" t="s">
+      <c r="C43" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="D43" s="54">
+      <c r="D43" s="60">
         <v>15000</v>
       </c>
-      <c r="E43" s="54"/>
-      <c r="F43" s="55">
+      <c r="E43" s="60">
+        <v>0</v>
+      </c>
+      <c r="F43" s="61">
         <f t="shared" si="5"/>
         <v>15000</v>
       </c>
-      <c r="G43" s="56">
+      <c r="G43" s="62">
         <f t="shared" si="3"/>
         <v>1500</v>
       </c>
-      <c r="H43" s="56">
+      <c r="H43" s="62">
         <f t="shared" si="4"/>
         <v>13500</v>
       </c>
-      <c r="I43" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="53">
+      <c r="I43" s="60" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="59">
         <v>45841</v>
       </c>
-      <c r="B44" s="54" t="s">
+      <c r="B44" s="60" t="s">
         <v>101</v>
       </c>
-      <c r="C44" s="54" t="s">
+      <c r="C44" s="60" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="52">
+      <c r="D44" s="63">
         <v>16100</v>
       </c>
-      <c r="E44" s="54">
+      <c r="E44" s="60">
         <v>7000</v>
       </c>
-      <c r="F44" s="55">
+      <c r="F44" s="61">
         <f t="shared" si="5"/>
         <v>23100</v>
       </c>
-      <c r="G44" s="56">
+      <c r="G44" s="62">
         <f t="shared" si="3"/>
         <v>2310</v>
       </c>
-      <c r="H44" s="56">
+      <c r="H44" s="62">
         <f t="shared" si="4"/>
         <v>20790</v>
       </c>
-      <c r="I44" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="J44" s="9" t="str">
-        <f>"Cr "  &amp; SUMIF(I2:I70, "paid", H2:H70)</f>
-        <v>Cr 600255</v>
-      </c>
-      <c r="K44" s="2" t="str">
-        <f>"Dr " &amp;SUMIF(I2:I70, "pending", H2:H70)</f>
-        <v>Dr 367155</v>
-      </c>
-      <c r="L44" s="4">
-        <f>SUM(H2:H70)</f>
-        <v>967410</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="53">
+      <c r="I44" s="60" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="59">
         <v>45841</v>
       </c>
-      <c r="B45" s="54" t="s">
+      <c r="B45" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="54" t="s">
+      <c r="C45" s="60" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="52">
+      <c r="D45" s="63">
         <v>15600</v>
       </c>
-      <c r="E45" s="54">
+      <c r="E45" s="60">
         <v>1750</v>
       </c>
-      <c r="F45" s="54">
+      <c r="F45" s="60">
         <f>D45+E45</f>
         <v>17350</v>
       </c>
-      <c r="G45" s="54">
+      <c r="G45" s="60">
         <f>F45*10/100</f>
         <v>1735</v>
       </c>
-      <c r="H45" s="54">
+      <c r="H45" s="60">
         <f>F45-G45</f>
         <v>15615</v>
       </c>
-      <c r="I45" s="54" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="53">
+      <c r="I45" s="60" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="59">
         <v>45842</v>
       </c>
-      <c r="B46" s="54" t="s">
+      <c r="B46" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="54" t="s">
+      <c r="C46" s="60" t="s">
         <v>105</v>
       </c>
-      <c r="D46" s="52">
+      <c r="D46" s="63">
         <v>15000</v>
       </c>
-      <c r="E46" s="54"/>
-      <c r="F46" s="54">
-        <f t="shared" ref="F46:F48" si="6">D46+E46</f>
+      <c r="E46" s="60">
+        <v>0</v>
+      </c>
+      <c r="F46" s="60">
+        <f t="shared" ref="F46:F66" si="6">D46+E46</f>
         <v>15000</v>
       </c>
-      <c r="G46" s="54">
-        <f t="shared" ref="G46:G48" si="7">F46*10/100</f>
+      <c r="G46" s="60">
+        <f t="shared" ref="G46:G66" si="7">F46*10/100</f>
         <v>1500</v>
       </c>
-      <c r="H46" s="54">
-        <f t="shared" ref="H46:H48" si="8">F46-G46</f>
+      <c r="H46" s="60">
+        <f t="shared" ref="H46:H66" si="8">F46-G46</f>
         <v>13500</v>
       </c>
-      <c r="I46" s="54" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="53">
+      <c r="I46" s="60" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="59">
         <v>45844</v>
       </c>
-      <c r="B47" s="54" t="s">
+      <c r="B47" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="C47" s="54" t="s">
+      <c r="C47" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="52">
+      <c r="D47" s="63">
         <v>5000</v>
       </c>
-      <c r="E47" s="54">
+      <c r="E47" s="60">
         <v>500</v>
       </c>
-      <c r="F47" s="54">
+      <c r="F47" s="60">
         <f t="shared" si="6"/>
         <v>5500</v>
       </c>
-      <c r="G47" s="54">
+      <c r="G47" s="60">
         <f t="shared" si="7"/>
         <v>550</v>
       </c>
-      <c r="H47" s="54">
+      <c r="H47" s="60">
         <f t="shared" si="8"/>
         <v>4950</v>
       </c>
-      <c r="I47" s="54" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="53">
+      <c r="I47" s="60" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="59">
         <v>45846</v>
       </c>
-      <c r="B48" s="54" t="s">
+      <c r="B48" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="54" t="s">
+      <c r="C48" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="D48" s="54">
+      <c r="D48" s="60">
         <v>17000</v>
       </c>
-      <c r="E48" s="54">
+      <c r="E48" s="60">
         <v>5000</v>
       </c>
-      <c r="F48" s="54">
+      <c r="F48" s="60">
         <f t="shared" si="6"/>
         <v>22000</v>
       </c>
-      <c r="G48" s="54">
+      <c r="G48" s="60">
         <f t="shared" si="7"/>
         <v>2200</v>
       </c>
-      <c r="H48" s="54">
+      <c r="H48" s="60">
         <f t="shared" si="8"/>
         <v>19800</v>
       </c>
-      <c r="I48" s="54" t="s">
+      <c r="I48" s="60" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="59">
+        <v>45851</v>
+      </c>
+      <c r="B49" s="60" t="s">
+        <v>110</v>
+      </c>
+      <c r="C49" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="D49" s="63">
+        <v>17000</v>
+      </c>
+      <c r="E49" s="60">
+        <v>5000</v>
+      </c>
+      <c r="F49" s="60">
+        <f t="shared" si="6"/>
+        <v>22000</v>
+      </c>
+      <c r="G49" s="60">
+        <f t="shared" si="7"/>
+        <v>2200</v>
+      </c>
+      <c r="H49" s="60">
+        <f t="shared" si="8"/>
+        <v>19800</v>
+      </c>
+      <c r="I49" s="60" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="6"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="6"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="6"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="6"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="6"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="6"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="6"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="6"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="6"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="6"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="6"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="6"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64"/>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="59">
+        <v>45852</v>
+      </c>
+      <c r="B50" s="60" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" s="60" t="s">
+        <v>113</v>
+      </c>
+      <c r="D50" s="63">
+        <v>40000</v>
+      </c>
+      <c r="E50" s="60">
+        <v>18000</v>
+      </c>
+      <c r="F50" s="60">
+        <f t="shared" si="6"/>
+        <v>58000</v>
+      </c>
+      <c r="G50" s="60">
+        <f t="shared" si="7"/>
+        <v>5800</v>
+      </c>
+      <c r="H50" s="60">
+        <f t="shared" si="8"/>
+        <v>52200</v>
+      </c>
+      <c r="I50" s="60" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="59">
+        <v>45855</v>
+      </c>
+      <c r="B51" s="60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="D51" s="63">
+        <v>15000</v>
+      </c>
+      <c r="E51" s="60">
+        <v>0</v>
+      </c>
+      <c r="F51" s="60">
+        <f t="shared" si="6"/>
+        <v>15000</v>
+      </c>
+      <c r="G51" s="60">
+        <f t="shared" si="7"/>
+        <v>1500</v>
+      </c>
+      <c r="H51" s="60">
+        <f t="shared" si="8"/>
+        <v>13500</v>
+      </c>
+      <c r="I51" s="60" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="59">
+        <v>45855</v>
+      </c>
+      <c r="B52" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="C52" s="60" t="s">
+        <v>116</v>
+      </c>
+      <c r="D52" s="60">
+        <v>15000</v>
+      </c>
+      <c r="E52" s="60">
+        <v>0</v>
+      </c>
+      <c r="F52" s="60">
+        <f t="shared" si="6"/>
+        <v>15000</v>
+      </c>
+      <c r="G52" s="60">
+        <f t="shared" si="7"/>
+        <v>1500</v>
+      </c>
+      <c r="H52" s="60">
+        <f t="shared" si="8"/>
+        <v>13500</v>
+      </c>
+      <c r="I52" s="60" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="59">
+        <v>45858</v>
+      </c>
+      <c r="B53" s="60" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" s="60" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53" s="60">
+        <v>5000</v>
+      </c>
+      <c r="E53" s="60">
+        <v>0</v>
+      </c>
+      <c r="F53" s="60">
+        <f t="shared" si="6"/>
+        <v>5000</v>
+      </c>
+      <c r="G53" s="60">
+        <f t="shared" si="7"/>
+        <v>500</v>
+      </c>
+      <c r="H53" s="60">
+        <f t="shared" si="8"/>
+        <v>4500</v>
+      </c>
+      <c r="I53" s="60" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="59">
+        <v>45864</v>
+      </c>
+      <c r="B54" s="60" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="60" t="s">
+        <v>120</v>
+      </c>
+      <c r="D54" s="60">
+        <v>5000</v>
+      </c>
+      <c r="E54" s="60">
+        <v>0</v>
+      </c>
+      <c r="F54" s="60">
+        <f t="shared" si="6"/>
+        <v>5000</v>
+      </c>
+      <c r="G54" s="60">
+        <f t="shared" si="7"/>
+        <v>500</v>
+      </c>
+      <c r="H54" s="60">
+        <f t="shared" si="8"/>
+        <v>4500</v>
+      </c>
+      <c r="I54" s="60" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="59">
+        <v>45867</v>
+      </c>
+      <c r="B55" s="60" t="s">
+        <v>121</v>
+      </c>
+      <c r="C55" s="60" t="s">
+        <v>122</v>
+      </c>
+      <c r="D55" s="60">
+        <v>26800</v>
+      </c>
+      <c r="E55" s="60">
+        <v>7000</v>
+      </c>
+      <c r="F55" s="60">
+        <f t="shared" si="6"/>
+        <v>33800</v>
+      </c>
+      <c r="G55" s="60">
+        <f t="shared" si="7"/>
+        <v>3380</v>
+      </c>
+      <c r="H55" s="60">
+        <f t="shared" si="8"/>
+        <v>30420</v>
+      </c>
+      <c r="I55" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="J55" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="K55" s="56"/>
+      <c r="L55" s="56"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="58">
+        <v>45887</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D56" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2">
+        <f t="shared" si="6"/>
+        <v>5000</v>
+      </c>
+      <c r="G56" s="2">
+        <f t="shared" si="7"/>
+        <v>500</v>
+      </c>
+      <c r="H56" s="2">
+        <f t="shared" si="8"/>
+        <v>4500</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J56" s="9"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="58">
+        <v>45897</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D57" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2">
+        <f t="shared" si="6"/>
+        <v>5000</v>
+      </c>
+      <c r="G57" s="2">
+        <f t="shared" si="7"/>
+        <v>500</v>
+      </c>
+      <c r="H57" s="2">
+        <f t="shared" si="8"/>
+        <v>4500</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="58">
+        <v>45900</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D58" s="2">
+        <v>12000</v>
+      </c>
+      <c r="E58" s="2">
+        <v>2000</v>
+      </c>
+      <c r="F58" s="2">
+        <f t="shared" si="6"/>
+        <v>14000</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="7"/>
+        <v>1400</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="8"/>
+        <v>12600</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J58" s="10" t="str">
+        <f>"Dr " &amp; SUMIF(I2:I70,"paid",G2:G70)</f>
+        <v>Dr 103220</v>
+      </c>
+      <c r="K58" s="3" t="str">
+        <f>"Cr " &amp; SUMIF(I2:I70,"pending",G2:G70)</f>
+        <v>Cr 46180</v>
+      </c>
+      <c r="L58" s="4">
+        <f>SUM(G2:G70)</f>
+        <v>149400</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="58">
+        <v>45908</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D59" s="2">
+        <v>25000</v>
+      </c>
+      <c r="E59" s="2">
+        <v>15000</v>
+      </c>
+      <c r="F59" s="2">
+        <f t="shared" si="6"/>
+        <v>40000</v>
+      </c>
+      <c r="G59" s="2">
+        <f t="shared" si="7"/>
+        <v>4000</v>
+      </c>
+      <c r="H59" s="2">
+        <f t="shared" si="8"/>
+        <v>36000</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J59" s="53"/>
+      <c r="K59" s="54"/>
+      <c r="L59" s="54"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" s="58">
+        <v>45908</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D60" s="2">
+        <v>46600</v>
+      </c>
+      <c r="E60" s="2">
+        <v>27000</v>
+      </c>
+      <c r="F60" s="2">
+        <f t="shared" si="6"/>
+        <v>73600</v>
+      </c>
+      <c r="G60" s="2">
+        <f t="shared" si="7"/>
+        <v>7360</v>
+      </c>
+      <c r="H60" s="2">
+        <f t="shared" si="8"/>
+        <v>66240</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" s="58">
+        <v>45910</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D61" s="2">
+        <v>20800</v>
+      </c>
+      <c r="E61" s="2">
+        <v>15000</v>
+      </c>
+      <c r="F61" s="2">
+        <f t="shared" si="6"/>
+        <v>35800</v>
+      </c>
+      <c r="G61" s="2">
+        <f t="shared" si="7"/>
+        <v>3580</v>
+      </c>
+      <c r="H61" s="2">
+        <f t="shared" si="8"/>
+        <v>32220</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J61" s="9" t="str">
+        <f>"Cr "  &amp; SUMIF(I2:I70, "paid", H2:H70)</f>
+        <v>Cr 928980</v>
+      </c>
+      <c r="K61" s="2" t="str">
+        <f>"Dr " &amp;SUMIF(I2:I70, "pending", H2:H70)</f>
+        <v>Dr 415620</v>
+      </c>
+      <c r="L61" s="4">
+        <f>SUM(H2:H70)</f>
+        <v>1344600</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" s="58">
+        <v>45910</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D62" s="48">
+        <v>17000</v>
+      </c>
+      <c r="E62" s="48">
+        <v>20000</v>
+      </c>
+      <c r="F62" s="2">
+        <f t="shared" si="6"/>
+        <v>37000</v>
+      </c>
+      <c r="G62" s="2">
+        <f t="shared" si="7"/>
+        <v>3700</v>
+      </c>
+      <c r="H62" s="2">
+        <f t="shared" si="8"/>
+        <v>33300</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" s="58">
+        <v>45914</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D63" s="2">
+        <v>19000</v>
+      </c>
+      <c r="E63" s="2">
+        <v>7000</v>
+      </c>
+      <c r="F63" s="2">
+        <f t="shared" si="6"/>
+        <v>26000</v>
+      </c>
+      <c r="G63" s="2">
+        <f t="shared" si="7"/>
+        <v>2600</v>
+      </c>
+      <c r="H63" s="2">
+        <f t="shared" si="8"/>
+        <v>23400</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" s="58">
+        <v>45915</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D64" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2">
+        <f t="shared" si="6"/>
+        <v>2000</v>
+      </c>
+      <c r="G64" s="2">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="H64" s="2">
+        <f t="shared" si="8"/>
+        <v>1800</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="58">
+        <v>45916</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D65" s="48">
+        <v>15500</v>
+      </c>
+      <c r="E65" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F65" s="2">
+        <f t="shared" si="6"/>
+        <v>21500</v>
+      </c>
+      <c r="G65" s="2">
+        <f t="shared" si="7"/>
+        <v>2150</v>
+      </c>
+      <c r="H65" s="2">
+        <f t="shared" si="8"/>
+        <v>19350</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="58">
+        <v>45919</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" s="48">
+        <v>18600</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2">
+        <f t="shared" si="6"/>
+        <v>18600</v>
+      </c>
+      <c r="G66" s="2">
+        <f t="shared" si="7"/>
+        <v>1860</v>
+      </c>
+      <c r="H66" s="2">
+        <f t="shared" si="8"/>
+        <v>16740</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="6"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="6"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="6"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="6"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="6"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="6"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="6"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="6"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="6"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="6"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="6"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="6"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="6"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="6"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
     </row>
   </sheetData>
   <sortState ref="A2:I24">
     <sortCondition ref="A1" customList="January,February,March,April,May,June,July,August,September,October,November,December"/>
   </sortState>
   <mergeCells count="2">
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J38:L38"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="J55:L55"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="72" orientation="landscape" r:id="rId1"/>
@@ -2683,11 +3415,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -2720,9 +3452,9 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="49"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
+      <c r="A5" s="54"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">

--- a/MAA-YOJANA-PACKAGELIST/Accounts/transactionDetails.xlsx
+++ b/MAA-YOJANA-PACKAGELIST/Accounts/transactionDetails.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="144">
   <si>
     <t>T.ID</t>
   </si>
@@ -444,6 +444,12 @@
   </si>
   <si>
     <t>Shiv Ji Ram Meena</t>
+  </si>
+  <si>
+    <t>T24092542381076</t>
+  </si>
+  <si>
+    <t>vijay Kumar</t>
   </si>
 </sst>
 </file>
@@ -723,6 +729,17 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -735,17 +752,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1140,7 +1146,7 @@
       <c r="A3" s="22">
         <v>45674</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="53" t="s">
         <v>35</v>
       </c>
       <c r="C3" s="24" t="s">
@@ -2385,460 +2391,460 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="59">
+      <c r="A42" s="55">
         <v>45839</v>
       </c>
-      <c r="B42" s="60" t="s">
+      <c r="B42" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="D42" s="60">
+      <c r="D42" s="56">
         <v>15600</v>
       </c>
-      <c r="E42" s="60">
+      <c r="E42" s="56">
         <v>10000</v>
       </c>
-      <c r="F42" s="61">
+      <c r="F42" s="57">
         <f t="shared" si="5"/>
         <v>25600</v>
       </c>
-      <c r="G42" s="62">
+      <c r="G42" s="58">
         <f t="shared" si="3"/>
         <v>2560</v>
       </c>
-      <c r="H42" s="62">
+      <c r="H42" s="58">
         <f t="shared" si="4"/>
         <v>23040</v>
       </c>
-      <c r="I42" s="60" t="s">
+      <c r="I42" s="56" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="59">
+      <c r="A43" s="55">
         <v>45840</v>
       </c>
-      <c r="B43" s="60" t="s">
+      <c r="B43" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="C43" s="60" t="s">
+      <c r="C43" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="D43" s="60">
+      <c r="D43" s="56">
         <v>15000</v>
       </c>
-      <c r="E43" s="60">
+      <c r="E43" s="56">
         <v>0</v>
       </c>
-      <c r="F43" s="61">
+      <c r="F43" s="57">
         <f t="shared" si="5"/>
         <v>15000</v>
       </c>
-      <c r="G43" s="62">
+      <c r="G43" s="58">
         <f t="shared" si="3"/>
         <v>1500</v>
       </c>
-      <c r="H43" s="62">
+      <c r="H43" s="58">
         <f t="shared" si="4"/>
         <v>13500</v>
       </c>
-      <c r="I43" s="60" t="s">
+      <c r="I43" s="56" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="59">
+      <c r="A44" s="55">
         <v>45841</v>
       </c>
-      <c r="B44" s="60" t="s">
+      <c r="B44" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C44" s="60" t="s">
+      <c r="C44" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="63">
+      <c r="D44" s="59">
         <v>16100</v>
       </c>
-      <c r="E44" s="60">
+      <c r="E44" s="56">
         <v>7000</v>
       </c>
-      <c r="F44" s="61">
+      <c r="F44" s="57">
         <f t="shared" si="5"/>
         <v>23100</v>
       </c>
-      <c r="G44" s="62">
+      <c r="G44" s="58">
         <f t="shared" si="3"/>
         <v>2310</v>
       </c>
-      <c r="H44" s="62">
+      <c r="H44" s="58">
         <f t="shared" si="4"/>
         <v>20790</v>
       </c>
-      <c r="I44" s="60" t="s">
+      <c r="I44" s="56" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="59">
+      <c r="A45" s="55">
         <v>45841</v>
       </c>
-      <c r="B45" s="60" t="s">
+      <c r="B45" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="60" t="s">
+      <c r="C45" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="63">
+      <c r="D45" s="59">
         <v>15600</v>
       </c>
-      <c r="E45" s="60">
+      <c r="E45" s="56">
         <v>1750</v>
       </c>
-      <c r="F45" s="60">
+      <c r="F45" s="56">
         <f>D45+E45</f>
         <v>17350</v>
       </c>
-      <c r="G45" s="60">
+      <c r="G45" s="56">
         <f>F45*10/100</f>
         <v>1735</v>
       </c>
-      <c r="H45" s="60">
+      <c r="H45" s="56">
         <f>F45-G45</f>
         <v>15615</v>
       </c>
-      <c r="I45" s="60" t="s">
+      <c r="I45" s="56" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="59">
+      <c r="A46" s="55">
         <v>45842</v>
       </c>
-      <c r="B46" s="60" t="s">
+      <c r="B46" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="D46" s="63">
+      <c r="D46" s="59">
         <v>15000</v>
       </c>
-      <c r="E46" s="60">
+      <c r="E46" s="56">
         <v>0</v>
       </c>
-      <c r="F46" s="60">
-        <f t="shared" ref="F46:F66" si="6">D46+E46</f>
+      <c r="F46" s="56">
+        <f t="shared" ref="F46:F67" si="6">D46+E46</f>
         <v>15000</v>
       </c>
-      <c r="G46" s="60">
-        <f t="shared" ref="G46:G66" si="7">F46*10/100</f>
+      <c r="G46" s="56">
+        <f t="shared" ref="G46:G67" si="7">F46*10/100</f>
         <v>1500</v>
       </c>
-      <c r="H46" s="60">
-        <f t="shared" ref="H46:H66" si="8">F46-G46</f>
+      <c r="H46" s="56">
+        <f t="shared" ref="H46:H67" si="8">F46-G46</f>
         <v>13500</v>
       </c>
-      <c r="I46" s="60" t="s">
+      <c r="I46" s="56" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="59">
+      <c r="A47" s="55">
         <v>45844</v>
       </c>
-      <c r="B47" s="60" t="s">
+      <c r="B47" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="C47" s="60" t="s">
+      <c r="C47" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="63">
+      <c r="D47" s="59">
         <v>5000</v>
       </c>
-      <c r="E47" s="60">
+      <c r="E47" s="56">
         <v>500</v>
       </c>
-      <c r="F47" s="60">
+      <c r="F47" s="56">
         <f t="shared" si="6"/>
         <v>5500</v>
       </c>
-      <c r="G47" s="60">
+      <c r="G47" s="56">
         <f t="shared" si="7"/>
         <v>550</v>
       </c>
-      <c r="H47" s="60">
+      <c r="H47" s="56">
         <f t="shared" si="8"/>
         <v>4950</v>
       </c>
-      <c r="I47" s="60" t="s">
+      <c r="I47" s="56" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="59">
+      <c r="A48" s="55">
         <v>45846</v>
       </c>
-      <c r="B48" s="60" t="s">
+      <c r="B48" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="60" t="s">
+      <c r="C48" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="D48" s="60">
+      <c r="D48" s="56">
         <v>17000</v>
       </c>
-      <c r="E48" s="60">
+      <c r="E48" s="56">
         <v>5000</v>
       </c>
-      <c r="F48" s="60">
+      <c r="F48" s="56">
         <f t="shared" si="6"/>
         <v>22000</v>
       </c>
-      <c r="G48" s="60">
+      <c r="G48" s="56">
         <f t="shared" si="7"/>
         <v>2200</v>
       </c>
-      <c r="H48" s="60">
+      <c r="H48" s="56">
         <f t="shared" si="8"/>
         <v>19800</v>
       </c>
-      <c r="I48" s="60" t="s">
+      <c r="I48" s="56" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="59">
+      <c r="A49" s="55">
         <v>45851</v>
       </c>
-      <c r="B49" s="60" t="s">
+      <c r="B49" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="C49" s="63" t="s">
+      <c r="C49" s="59" t="s">
         <v>111</v>
       </c>
-      <c r="D49" s="63">
+      <c r="D49" s="59">
         <v>17000</v>
       </c>
-      <c r="E49" s="60">
+      <c r="E49" s="56">
         <v>5000</v>
       </c>
-      <c r="F49" s="60">
+      <c r="F49" s="56">
         <f t="shared" si="6"/>
         <v>22000</v>
       </c>
-      <c r="G49" s="60">
+      <c r="G49" s="56">
         <f t="shared" si="7"/>
         <v>2200</v>
       </c>
-      <c r="H49" s="60">
+      <c r="H49" s="56">
         <f t="shared" si="8"/>
         <v>19800</v>
       </c>
-      <c r="I49" s="60" t="s">
+      <c r="I49" s="56" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="59">
+      <c r="A50" s="55">
         <v>45852</v>
       </c>
-      <c r="B50" s="60" t="s">
+      <c r="B50" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="C50" s="60" t="s">
+      <c r="C50" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="D50" s="63">
+      <c r="D50" s="59">
         <v>40000</v>
       </c>
-      <c r="E50" s="60">
+      <c r="E50" s="56">
         <v>18000</v>
       </c>
-      <c r="F50" s="60">
+      <c r="F50" s="56">
         <f t="shared" si="6"/>
         <v>58000</v>
       </c>
-      <c r="G50" s="60">
+      <c r="G50" s="56">
         <f t="shared" si="7"/>
         <v>5800</v>
       </c>
-      <c r="H50" s="60">
+      <c r="H50" s="56">
         <f t="shared" si="8"/>
         <v>52200</v>
       </c>
-      <c r="I50" s="60" t="s">
+      <c r="I50" s="56" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="59">
+      <c r="A51" s="55">
         <v>45855</v>
       </c>
-      <c r="B51" s="60" t="s">
+      <c r="B51" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="C51" s="60" t="s">
+      <c r="C51" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="D51" s="63">
+      <c r="D51" s="59">
         <v>15000</v>
       </c>
-      <c r="E51" s="60">
+      <c r="E51" s="56">
         <v>0</v>
       </c>
-      <c r="F51" s="60">
+      <c r="F51" s="56">
         <f t="shared" si="6"/>
         <v>15000</v>
       </c>
-      <c r="G51" s="60">
+      <c r="G51" s="56">
         <f t="shared" si="7"/>
         <v>1500</v>
       </c>
-      <c r="H51" s="60">
+      <c r="H51" s="56">
         <f t="shared" si="8"/>
         <v>13500</v>
       </c>
-      <c r="I51" s="60" t="s">
+      <c r="I51" s="56" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="59">
+      <c r="A52" s="55">
         <v>45855</v>
       </c>
-      <c r="B52" s="60" t="s">
+      <c r="B52" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="C52" s="60" t="s">
+      <c r="C52" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="D52" s="60">
+      <c r="D52" s="56">
         <v>15000</v>
       </c>
-      <c r="E52" s="60">
+      <c r="E52" s="56">
         <v>0</v>
       </c>
-      <c r="F52" s="60">
+      <c r="F52" s="56">
         <f t="shared" si="6"/>
         <v>15000</v>
       </c>
-      <c r="G52" s="60">
+      <c r="G52" s="56">
         <f t="shared" si="7"/>
         <v>1500</v>
       </c>
-      <c r="H52" s="60">
+      <c r="H52" s="56">
         <f t="shared" si="8"/>
         <v>13500</v>
       </c>
-      <c r="I52" s="60" t="s">
+      <c r="I52" s="56" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="59">
+      <c r="A53" s="55">
         <v>45858</v>
       </c>
-      <c r="B53" s="60" t="s">
+      <c r="B53" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="C53" s="60" t="s">
+      <c r="C53" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="D53" s="60">
+      <c r="D53" s="56">
         <v>5000</v>
       </c>
-      <c r="E53" s="60">
+      <c r="E53" s="56">
         <v>0</v>
       </c>
-      <c r="F53" s="60">
+      <c r="F53" s="56">
         <f t="shared" si="6"/>
         <v>5000</v>
       </c>
-      <c r="G53" s="60">
+      <c r="G53" s="56">
         <f t="shared" si="7"/>
         <v>500</v>
       </c>
-      <c r="H53" s="60">
+      <c r="H53" s="56">
         <f t="shared" si="8"/>
         <v>4500</v>
       </c>
-      <c r="I53" s="60" t="s">
+      <c r="I53" s="56" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="59">
+      <c r="A54" s="55">
         <v>45864</v>
       </c>
-      <c r="B54" s="60" t="s">
+      <c r="B54" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="C54" s="60" t="s">
+      <c r="C54" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="D54" s="60">
+      <c r="D54" s="56">
         <v>5000</v>
       </c>
-      <c r="E54" s="60">
+      <c r="E54" s="56">
         <v>0</v>
       </c>
-      <c r="F54" s="60">
+      <c r="F54" s="56">
         <f t="shared" si="6"/>
         <v>5000</v>
       </c>
-      <c r="G54" s="60">
+      <c r="G54" s="56">
         <f t="shared" si="7"/>
         <v>500</v>
       </c>
-      <c r="H54" s="60">
+      <c r="H54" s="56">
         <f t="shared" si="8"/>
         <v>4500</v>
       </c>
-      <c r="I54" s="60" t="s">
+      <c r="I54" s="56" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="59">
+      <c r="A55" s="55">
         <v>45867</v>
       </c>
-      <c r="B55" s="60" t="s">
+      <c r="B55" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="C55" s="60" t="s">
+      <c r="C55" s="56" t="s">
         <v>122</v>
       </c>
-      <c r="D55" s="60">
+      <c r="D55" s="56">
         <v>26800</v>
       </c>
-      <c r="E55" s="60">
+      <c r="E55" s="56">
         <v>7000</v>
       </c>
-      <c r="F55" s="60">
+      <c r="F55" s="56">
         <f t="shared" si="6"/>
         <v>33800</v>
       </c>
-      <c r="G55" s="60">
+      <c r="G55" s="56">
         <f t="shared" si="7"/>
         <v>3380</v>
       </c>
-      <c r="H55" s="60">
+      <c r="H55" s="56">
         <f t="shared" si="8"/>
         <v>30420</v>
       </c>
-      <c r="I55" s="60" t="s">
-        <v>30</v>
-      </c>
-      <c r="J55" s="55" t="s">
+      <c r="I55" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="J55" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="K55" s="56"/>
-      <c r="L55" s="56"/>
+      <c r="K55" s="63"/>
+      <c r="L55" s="63"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="58">
+      <c r="A56" s="54">
         <v>45887</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -2873,7 +2879,7 @@
       <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="58">
+      <c r="A57" s="54">
         <v>45897</v>
       </c>
       <c r="B57" s="2" t="s">
@@ -2914,7 +2920,7 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="58">
+      <c r="A58" s="54">
         <v>45900</v>
       </c>
       <c r="B58" s="2" t="s">
@@ -2950,15 +2956,15 @@
       </c>
       <c r="K58" s="3" t="str">
         <f>"Cr " &amp; SUMIF(I2:I70,"pending",G2:G70)</f>
-        <v>Cr 46180</v>
+        <v>Cr 51980</v>
       </c>
       <c r="L58" s="4">
         <f>SUM(G2:G70)</f>
-        <v>149400</v>
+        <v>155200</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="58">
+      <c r="A59" s="54">
         <v>45908</v>
       </c>
       <c r="B59" s="2" t="s">
@@ -2988,12 +2994,12 @@
       <c r="I59" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J59" s="53"/>
-      <c r="K59" s="54"/>
-      <c r="L59" s="54"/>
+      <c r="J59" s="60"/>
+      <c r="K59" s="61"/>
+      <c r="L59" s="61"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="58">
+      <c r="A60" s="54">
         <v>45908</v>
       </c>
       <c r="B60" s="2" t="s">
@@ -3034,7 +3040,7 @@
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="58">
+      <c r="A61" s="54">
         <v>45910</v>
       </c>
       <c r="B61" s="2" t="s">
@@ -3070,15 +3076,15 @@
       </c>
       <c r="K61" s="2" t="str">
         <f>"Dr " &amp;SUMIF(I2:I70, "pending", H2:H70)</f>
-        <v>Dr 415620</v>
+        <v>Dr 467820</v>
       </c>
       <c r="L61" s="4">
         <f>SUM(H2:H70)</f>
-        <v>1344600</v>
+        <v>1396800</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="58">
+      <c r="A62" s="54">
         <v>45910</v>
       </c>
       <c r="B62" s="2" t="s">
@@ -3110,7 +3116,7 @@
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="58">
+      <c r="A63" s="54">
         <v>45914</v>
       </c>
       <c r="B63" s="2" t="s">
@@ -3142,7 +3148,7 @@
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="58">
+      <c r="A64" s="54">
         <v>45915</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -3174,7 +3180,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="58">
+      <c r="A65" s="54">
         <v>45916</v>
       </c>
       <c r="B65" s="2" t="s">
@@ -3206,7 +3212,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="58">
+      <c r="A66" s="54">
         <v>45919</v>
       </c>
       <c r="B66" s="2" t="s">
@@ -3238,15 +3244,36 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="6"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
+      <c r="A67" s="54">
+        <v>45924</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D67" s="2">
+        <v>40000</v>
+      </c>
+      <c r="E67" s="2">
+        <v>18000</v>
+      </c>
+      <c r="F67" s="2">
+        <f t="shared" si="6"/>
+        <v>58000</v>
+      </c>
+      <c r="G67" s="2">
+        <f t="shared" si="7"/>
+        <v>5800</v>
+      </c>
+      <c r="H67" s="2">
+        <f t="shared" si="8"/>
+        <v>52200</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
@@ -3415,11 +3442,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -3452,9 +3479,9 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="54"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">

--- a/MAA-YOJANA-PACKAGELIST/Accounts/transactionDetails.xlsx
+++ b/MAA-YOJANA-PACKAGELIST/Accounts/transactionDetails.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="146">
   <si>
     <t>T.ID</t>
   </si>
@@ -450,6 +450,12 @@
   </si>
   <si>
     <t>vijay Kumar</t>
+  </si>
+  <si>
+    <t>Teel Singh Rawat</t>
+  </si>
+  <si>
+    <t>T27092542449532</t>
   </si>
 </sst>
 </file>
@@ -2003,7 +2009,7 @@
         <v>59400</v>
       </c>
       <c r="I29" s="40" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -2535,15 +2541,15 @@
         <v>0</v>
       </c>
       <c r="F46" s="56">
-        <f t="shared" ref="F46:F67" si="6">D46+E46</f>
+        <f t="shared" ref="F46:F68" si="6">D46+E46</f>
         <v>15000</v>
       </c>
       <c r="G46" s="56">
-        <f t="shared" ref="G46:G67" si="7">F46*10/100</f>
+        <f t="shared" ref="G46:G68" si="7">F46*10/100</f>
         <v>1500</v>
       </c>
       <c r="H46" s="56">
-        <f t="shared" ref="H46:H67" si="8">F46-G46</f>
+        <f t="shared" ref="H46:H68" si="8">F46-G46</f>
         <v>13500</v>
       </c>
       <c r="I46" s="56" t="s">
@@ -2948,19 +2954,19 @@
         <v>12600</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J58" s="10" t="str">
         <f>"Dr " &amp; SUMIF(I2:I70,"paid",G2:G70)</f>
-        <v>Dr 103220</v>
+        <v>Dr 134810</v>
       </c>
       <c r="K58" s="3" t="str">
         <f>"Cr " &amp; SUMIF(I2:I70,"pending",G2:G70)</f>
-        <v>Cr 51980</v>
+        <v>Cr 23690</v>
       </c>
       <c r="L58" s="4">
         <f>SUM(G2:G70)</f>
-        <v>155200</v>
+        <v>158500</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -2992,7 +2998,7 @@
         <v>36000</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J59" s="60"/>
       <c r="K59" s="61"/>
@@ -3027,7 +3033,7 @@
         <v>66240</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J60" s="9" t="s">
         <v>26</v>
@@ -3068,19 +3074,19 @@
         <v>32220</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J61" s="9" t="str">
         <f>"Cr "  &amp; SUMIF(I2:I70, "paid", H2:H70)</f>
-        <v>Cr 928980</v>
+        <v>Cr 1213290</v>
       </c>
       <c r="K61" s="2" t="str">
         <f>"Dr " &amp;SUMIF(I2:I70, "pending", H2:H70)</f>
-        <v>Dr 467820</v>
+        <v>Dr 213210</v>
       </c>
       <c r="L61" s="4">
         <f>SUM(H2:H70)</f>
-        <v>1396800</v>
+        <v>1426500</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3112,7 +3118,7 @@
         <v>33300</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3144,7 +3150,7 @@
         <v>23400</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3176,7 +3182,7 @@
         <v>1800</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -3208,7 +3214,7 @@
         <v>19350</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -3276,15 +3282,36 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="6"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
+      <c r="A68" s="54">
+        <v>45927</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D68" s="48">
+        <v>19000</v>
+      </c>
+      <c r="E68" s="2">
+        <v>14000</v>
+      </c>
+      <c r="F68" s="2">
+        <f t="shared" si="6"/>
+        <v>33000</v>
+      </c>
+      <c r="G68" s="2">
+        <f t="shared" si="7"/>
+        <v>3300</v>
+      </c>
+      <c r="H68" s="2">
+        <f t="shared" si="8"/>
+        <v>29700</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
@@ -3427,7 +3454,7 @@
     <mergeCell ref="J55:L55"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="72" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="43" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
